--- a/cnc_20240208/gantt_example.xlsx
+++ b/cnc_20240208/gantt_example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csucloudservices-my.sharepoint.com/personal/andrew_hood_mlcsu_nhs_uk/Documents/Working Projects/coffee_n_coding/cnc_20240208_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nhs-my.sharepoint.com/personal/andrewhood_nhs_net/Documents/coffee_n_coding/cnc_20240208/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{A7E53DE4-FC2D-4F28-9343-FB1AD2FA2960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97E27779-F15D-46BE-AB41-27A7E075E834}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="8_{A7E53DE4-FC2D-4F28-9343-FB1AD2FA2960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6413852F-C527-4299-BA17-409B0BB7025A}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="10620" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{0283D5F9-1C06-41CA-BC77-EB132DD15F99}"/>
+    <workbookView xWindow="-28920" yWindow="0" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0283D5F9-1C06-41CA-BC77-EB132DD15F99}"/>
   </bookViews>
   <sheets>
     <sheet name="gantt" sheetId="1" r:id="rId1"/>
@@ -500,14 +500,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B039E2B3-E91C-44B7-A1D5-7BEA8A65727A}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.6796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.453125" customWidth="1"/>
+    <col min="2" max="2" width="25.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -521,7 +521,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -535,7 +535,7 @@
         <v>45303</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -549,7 +549,7 @@
         <v>45303</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -563,7 +563,7 @@
         <v>45303</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -577,7 +577,7 @@
         <v>45317</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -591,7 +591,7 @@
         <v>45324</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -605,7 +605,7 @@
         <v>45338</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -619,7 +619,7 @@
         <v>45345</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -633,7 +633,7 @@
         <v>45345</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -647,7 +647,7 @@
         <v>45352</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -661,7 +661,7 @@
         <v>45366</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -675,7 +675,7 @@
         <v>45380</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -689,7 +689,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -703,7 +703,7 @@
         <v>45394</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -717,7 +717,7 @@
         <v>45408</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -731,7 +731,7 @@
         <v>45429</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -753,14 +753,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD23B30-054E-4890-87CC-BA9F357E9A80}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.58984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.76953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -771,7 +771,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -782,7 +782,7 @@
         <v>45294</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -793,7 +793,7 @@
         <v>45337</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -804,7 +804,7 @@
         <v>45350</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -815,7 +815,7 @@
         <v>45393</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -826,7 +826,7 @@
         <v>45432</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
